--- a/data/trans_dic/IP25B_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP25B_1_R-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,06; 24,03</t>
+          <t>10,95; 24,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,11; 31,05</t>
+          <t>12,63; 31,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 26,38</t>
+          <t>14,35; 26,17</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 25,69</t>
+          <t>11,74; 26,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,64; 26,06</t>
+          <t>11,48; 25,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,05; 24,53</t>
+          <t>13,69; 23,37</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 38,75</t>
+          <t>14,78; 36,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 37,23</t>
+          <t>17,27; 37,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 34,18</t>
+          <t>18,18; 33,62</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,15; 56,08</t>
+          <t>18,58; 54,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 35,75</t>
+          <t>21,81; 34,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 42,85</t>
+          <t>22,64; 45,9</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,45; 38,76</t>
+          <t>22,95; 40,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,45; 46,14</t>
+          <t>21,84; 45,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,75; 40,87</t>
+          <t>24,89; 39,54</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 29,43</t>
+          <t>12,37; 29,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 23,21</t>
+          <t>8,02; 24,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,94; 23,74</t>
+          <t>11,84; 23,84</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,38; 35,65</t>
+          <t>20,61; 35,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,92; 28,71</t>
+          <t>20,5; 28,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,79; 29,45</t>
+          <t>21,66; 30,64</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12216; 24339</t>
+          <t>11094; 24439</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17727; 41976</t>
+          <t>17074; 43143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33783; 62393</t>
+          <t>33934; 61888</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11573; 23804</t>
+          <t>10876; 24286</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12076; 24910</t>
+          <t>10976; 24770</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26439; 46185</t>
+          <t>25770; 43997</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8013; 19834</t>
+          <t>7565; 18628</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10478; 23772</t>
+          <t>11027; 23929</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21250; 39322</t>
+          <t>20910; 38676</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38944; 120316</t>
+          <t>39862; 117970</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46878; 77349</t>
+          <t>47176; 75607</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95044; 184614</t>
+          <t>97535; 197766</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26155; 45166</t>
+          <t>26748; 46853</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35855; 73708</t>
+          <t>34894; 73355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68367; 112900</t>
+          <t>68753; 109239</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8507; 19656</t>
+          <t>8264; 19470</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5739; 16621</t>
+          <t>5743; 17436</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16524; 32852</t>
+          <t>16382; 32994</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>131054; 229211</t>
+          <t>132512; 230320</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>155278; 213094</t>
+          <t>152194; 210953</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>301917; 408018</t>
+          <t>300047; 424401</t>
         </is>
       </c>
     </row>
